--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484680_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484680_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.520099999999999</v>
+        <v>8.309200000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>9.457599999999999</v>
+        <v>7.9742</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0625</v>
+        <v>0.335</v>
       </c>
       <c r="G2" t="n">
         <v>6.1933</v>
@@ -610,13 +610,13 @@
         <v>1.6493</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4343</v>
+        <v>1.2234</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8198</v>
+        <v>1.3364</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3855</v>
+        <v>-0.113</v>
       </c>
       <c r="V2" t="n">
         <v>0.3428</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5448</v>
+        <v>5.5862</v>
       </c>
       <c r="E3" t="n">
-        <v>6.092</v>
+        <v>5.0343</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4528</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>2.7464</v>
@@ -688,13 +688,13 @@
         <v>2.1991</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7146</v>
+        <v>0.756</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0136</v>
+        <v>0.9559</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.299</v>
+        <v>-0.1999</v>
       </c>
       <c r="V3" t="n">
         <v>1.9005</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5288</v>
+        <v>5.0125</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7749</v>
+        <v>4.1595</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7539</v>
+        <v>0.853</v>
       </c>
       <c r="G4" t="n">
         <v>3.0146</v>
@@ -766,13 +766,13 @@
         <v>2.1991</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2085</v>
+        <v>0.2753</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0905</v>
+        <v>0.4751</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.299</v>
+        <v>-0.1999</v>
       </c>
       <c r="V4" t="n">
         <v>0.6231</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9168</v>
+        <v>3.1449</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0736</v>
+        <v>3.376</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1568</v>
+        <v>-0.2311</v>
       </c>
       <c r="G5" t="n">
         <v>3.8185</v>
@@ -844,13 +844,13 @@
         <v>2.0158</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2683</v>
+        <v>-0.0402</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3122</v>
+        <v>-0.0098</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0439</v>
+        <v>-0.0304</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6335</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. MONTAÑO LINARES</t>
+          <t>B. MONDRAGON VIDAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9256</v>
+        <v>2.1646</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9256</v>
+        <v>1.5359</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.6287</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9256</v>
+        <v>3.0521</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3005</v>
+        <v>0.3016</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6251</v>
+        <v>2.7505</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9256</v>
+        <v>4.4277</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3005</v>
+        <v>1.709</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6251</v>
+        <v>2.7187</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-1.3756</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-1.4074</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.0318</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.1154</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.1991</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.0288</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.2236</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.1948</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. MONDRAGON VIDAL</t>
+          <t>K. MONTAÑO LINARES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8463</v>
+        <v>1.9256</v>
       </c>
       <c r="E7" t="n">
-        <v>0.945</v>
+        <v>1.9256</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9012</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0521</v>
+        <v>1.9256</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3016</v>
+        <v>1.3005</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7505</v>
+        <v>0.6251</v>
       </c>
       <c r="J7" t="n">
-        <v>4.4277</v>
+        <v>1.9256</v>
       </c>
       <c r="K7" t="n">
-        <v>1.709</v>
+        <v>1.3005</v>
       </c>
       <c r="L7" t="n">
-        <v>2.7187</v>
+        <v>0.6251</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3756</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4074</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0318</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.1154</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1991</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2895</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3673</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.07770000000000001</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2685</v>
+        <v>1.5902</v>
       </c>
       <c r="E8" t="n">
-        <v>0.236</v>
+        <v>0.4834</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0325</v>
+        <v>1.1068</v>
       </c>
       <c r="G8" t="n">
         <v>2.3365</v>
@@ -1078,13 +1078,13 @@
         <v>1.2828</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0417</v>
+        <v>0.28</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0369</v>
+        <v>0.2104</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0048</v>
+        <v>0.0696</v>
       </c>
       <c r="V8" t="n">
         <v>0.6231</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.229</v>
+        <v>1.5125</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3172</v>
+        <v>2.4273</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0882</v>
+        <v>-0.9147999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>1.6472</v>
@@ -1156,13 +1156,13 @@
         <v>0.733</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5073</v>
+        <v>-0.2238</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1652</v>
+        <v>-0.0551</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3422</v>
+        <v>-0.1687</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6439</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. PAÑOS HUERTAS</t>
+          <t>J. BALLESTER FERRANDIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6502</v>
+        <v>1.2631</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6502</v>
+        <v>1.1325</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.1306</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6502</v>
+        <v>2.3038</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6502</v>
+        <v>-0.5654</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2.8692</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6502</v>
+        <v>3.6947</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6502</v>
+        <v>0.4085</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.2862</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-1.391</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-0.9739</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0.417</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.9321</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.8326</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.3808</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.3699</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.0109</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. BALLESTER FERRANDIS</t>
+          <t>M. PAÑOS HUERTAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1941</v>
+        <v>0.6502</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2121</v>
+        <v>0.6502</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0181</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.3038</v>
+        <v>0.6502</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5654</v>
+        <v>0.6502</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8692</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6947</v>
+        <v>0.6502</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4085</v>
+        <v>0.6502</v>
       </c>
       <c r="L11" t="n">
-        <v>3.2862</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.391</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9739</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.417</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9321</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8326</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6882</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5505</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1377</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. AZNAR MARTINEZ</t>
+          <t>M. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0977</v>
+        <v>-0.0843</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2323</v>
+        <v>-0.9456</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.33</v>
+        <v>0.8613</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2233</v>
+        <v>0.6237</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8707</v>
+        <v>0.7872</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6474</v>
+        <v>-0.1635</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7828000000000001</v>
+        <v>1.372</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6161</v>
+        <v>1.2788</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1667</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.006</v>
+        <v>-0.7483</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4867</v>
+        <v>-0.4916</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4807</v>
+        <v>-0.2567</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1833</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0995</v>
+        <v>-2.7489</v>
       </c>
       <c r="R12" t="n">
         <v>1.2828</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2642</v>
+        <v>0.4361</v>
       </c>
       <c r="T12" t="n">
-        <v>0.549</v>
+        <v>0.1094</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2848</v>
+        <v>0.3267</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3219</v>
+        <v>0.3219</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. MONTANO LINARES</t>
+          <t>A. AZNAR MARTINEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4372</v>
+        <v>-0.1274</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5792</v>
+        <v>0.0539</v>
       </c>
       <c r="F13" t="n">
-        <v>0.142</v>
+        <v>-0.1813</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7439</v>
+        <v>-0.2233</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9389</v>
+        <v>-0.8707</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.6829</v>
+        <v>0.6474</v>
       </c>
       <c r="J13" t="n">
-        <v>1.233</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9477</v>
+        <v>0.6161</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.7147</v>
+        <v>0.1667</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.9769</v>
+        <v>-1.006</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.0088</v>
+        <v>-1.4867</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0318</v>
+        <v>0.4807</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.2828</v>
+        <v>0.1833</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.9321</v>
+        <v>-1.0995</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9665</v>
+        <v>0.2345</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1471</v>
+        <v>0.3707</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1135</v>
+        <v>-0.1361</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6231</v>
+        <v>-0.3219</v>
       </c>
       <c r="W13" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6439</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. PANOS HUERTAS</t>
+          <t>K. MONTANO LINARES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.4992</v>
+        <v>-0.5315</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.3852</v>
+        <v>-0.0294</v>
       </c>
       <c r="F14" t="n">
-        <v>0.886</v>
+        <v>-0.5021</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6237</v>
+        <v>-0.7439</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7872</v>
+        <v>0.9389</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1635</v>
+        <v>-1.6829</v>
       </c>
       <c r="J14" t="n">
-        <v>1.372</v>
+        <v>1.233</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2788</v>
+        <v>2.9477</v>
       </c>
       <c r="L14" t="n">
-        <v>0.09320000000000001</v>
+        <v>-1.7147</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7483</v>
+        <v>-1.9769</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4916</v>
+        <v>-2.0088</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2567</v>
+        <v>0.0318</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.4661</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.7489</v>
+        <v>-2.9321</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2828</v>
+        <v>1.6493</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0212</v>
+        <v>0.8721</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3303</v>
+        <v>0.4027</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3515</v>
+        <v>0.4694</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3219</v>
+        <v>0.6231</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3219</v>
+        <v>1.267</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>29.5901</v>
+        <v>30.4158</v>
       </c>
       <c r="E15" t="n">
-        <v>26.9521</v>
+        <v>27.7778</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6378</v>
+        <v>2.638</v>
       </c>
       <c r="G15" t="n">
         <v>27.3447</v>
@@ -1624,13 +1624,13 @@
         <v>18.3257</v>
       </c>
       <c r="S15" t="n">
-        <v>3.397299999999999</v>
+        <v>4.223</v>
       </c>
       <c r="T15" t="n">
-        <v>3.563399999999999</v>
+        <v>4.3892</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1664</v>
+        <v>-0.1662</v>
       </c>
       <c r="V15" t="n">
         <v>2.5133</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2914</v>
+        <v>0.035</v>
       </c>
       <c r="E18" t="n">
-        <v>4.7159</v>
+        <v>4.3313</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.4246</v>
+        <v>-4.2963</v>
       </c>
       <c r="G18" t="n">
         <v>-1.1997</v>
@@ -1858,13 +1858,13 @@
         <v>2.3823</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3469</v>
+        <v>0.0905</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6026</v>
+        <v>0.218</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2557</v>
+        <v>-0.1275</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3219</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. ALVAREZ LABRADOR</t>
+          <t>L. ALBEROLA GUILLOT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1647</v>
+        <v>-0.1139</v>
       </c>
       <c r="E19" t="n">
-        <v>1.794</v>
+        <v>1.3719</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6292</v>
+        <v>-1.4858</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2486</v>
+        <v>-0.9378</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0242</v>
+        <v>0.0239</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7756</v>
+        <v>-0.9617</v>
       </c>
       <c r="J19" t="n">
-        <v>3.2592</v>
+        <v>1.5107</v>
       </c>
       <c r="K19" t="n">
-        <v>1.8423</v>
+        <v>2.1517</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4169</v>
+        <v>-0.641</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.5079</v>
+        <v>-2.4484</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.8665</v>
+        <v>-2.1278</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6413</v>
+        <v>-0.3207</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5498</v>
+        <v>1.0995</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1991</v>
+        <v>1.0995</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0181</v>
+        <v>-0.2756</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0166</v>
+        <v>-0.1387</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0015</v>
+        <v>-0.1369</v>
       </c>
       <c r="V19" t="n">
-        <v>0.945</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. ALBEROLA GUILLOT</t>
+          <t>P. ALVAREZ LABRADOR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.128</v>
+        <v>-0.3715</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5642</v>
+        <v>1.5055</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4362</v>
+        <v>-1.877</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9378</v>
+        <v>-0.2486</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0239</v>
+        <v>-1.0242</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9617</v>
+        <v>0.7756</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5107</v>
+        <v>3.2592</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1517</v>
+        <v>1.8423</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.641</v>
+        <v>1.4169</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.4484</v>
+        <v>-3.5079</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.1278</v>
+        <v>-2.8665</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3207</v>
+        <v>-0.6413</v>
       </c>
       <c r="P20" t="n">
-        <v>1.0995</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0995</v>
+        <v>2.1991</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0338</v>
+        <v>-0.5181</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0536</v>
+        <v>-0.2719</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0873</v>
+        <v>-0.2462</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.945</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. GARCIA BURGOS</t>
+          <t>M. SHALABI TORRES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6158</v>
+        <v>-1.0086</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4677</v>
+        <v>1.8953</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1481</v>
+        <v>-2.9039</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4032</v>
+        <v>-2.0018</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0348</v>
+        <v>-3.8323</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3684</v>
+        <v>1.8305</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0619</v>
+        <v>3.7531</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5264</v>
+        <v>0.3836</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.4645</v>
+        <v>3.3696</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4652</v>
+        <v>-5.7549</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.5612</v>
+        <v>-4.2159</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0961</v>
+        <v>-1.5391</v>
       </c>
       <c r="P21" t="n">
-        <v>1.2828</v>
+        <v>1.6493</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1991</v>
+        <v>3.4819</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5608</v>
+        <v>-0.6561</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3122</v>
+        <v>-0.0252</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2486</v>
+        <v>-0.6309</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9346</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3011</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. SHALABI TORRES</t>
+          <t>G. GARCIA BURGOS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0576</v>
+        <v>-1.4265</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2223</v>
+        <v>-0.1792</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.2798</v>
+        <v>-1.2472</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0018</v>
+        <v>-1.4032</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.8323</v>
+        <v>-1.0348</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8305</v>
+        <v>-0.3684</v>
       </c>
       <c r="J22" t="n">
-        <v>3.7531</v>
+        <v>1.0619</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3836</v>
+        <v>1.5264</v>
       </c>
       <c r="L22" t="n">
-        <v>3.3696</v>
+        <v>-0.4645</v>
       </c>
       <c r="M22" t="n">
-        <v>-5.7549</v>
+        <v>-2.4652</v>
       </c>
       <c r="N22" t="n">
-        <v>-4.2159</v>
+        <v>-2.5612</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5391</v>
+        <v>0.0961</v>
       </c>
       <c r="P22" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R22" t="n">
-        <v>3.4819</v>
+        <v>2.1991</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7051</v>
+        <v>-0.3714</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6983</v>
+        <v>-0.0237</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0068</v>
+        <v>-0.3477</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.9346</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4028</v>
+        <v>-2.8296</v>
       </c>
       <c r="E23" t="n">
-        <v>1.18</v>
+        <v>0.6992</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.5828</v>
+        <v>-3.5289</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5564</v>
@@ -2248,13 +2248,13 @@
         <v>2.0158</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7559</v>
+        <v>0.329</v>
       </c>
       <c r="T23" t="n">
-        <v>0.914</v>
+        <v>0.4333</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1582</v>
+        <v>-0.1043</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8692</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9213</v>
+        <v>-2.8718</v>
       </c>
       <c r="E24" t="n">
         <v>-1.3407</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5806</v>
+        <v>-1.5311</v>
       </c>
       <c r="G24" t="n">
         <v>-2.3308</v>
@@ -2326,13 +2326,13 @@
         <v>1.2828</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3523</v>
+        <v>-0.3028</v>
       </c>
       <c r="T24" t="n">
         <v>0.2368</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5891</v>
+        <v>-0.5396</v>
       </c>
       <c r="V24" t="n">
         <v>0.3115</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8563</v>
+        <v>-3.3478</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.5375</v>
+        <v>-1.1529</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3188</v>
+        <v>-2.1949</v>
       </c>
       <c r="G25" t="n">
         <v>-3.0219</v>
@@ -2404,13 +2404,13 @@
         <v>2.3823</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3842</v>
+        <v>-0.8757</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7526</v>
+        <v>-0.368</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-0.5077</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.3222</v>
+        <v>-3.6607</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.5997</v>
+        <v>-1.2151</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.7224</v>
+        <v>-2.4456</v>
       </c>
       <c r="G26" t="n">
         <v>-5.088</v>
@@ -2482,13 +2482,13 @@
         <v>1.6493</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5615</v>
+        <v>0.0999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3311</v>
+        <v>0.0536</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2305</v>
+        <v>0.0464</v>
       </c>
       <c r="V26" t="n">
         <v>-0.3219</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-6.8662</v>
+        <v>-7.0803</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.9983</v>
+        <v>-5.2868</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.8679</v>
+        <v>-1.7936</v>
       </c>
       <c r="G27" t="n">
         <v>-6.462</v>
@@ -2560,13 +2560,13 @@
         <v>1.6493</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.1714</v>
+        <v>-0.3855</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2368</v>
+        <v>-0.0516</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.4082</v>
+        <v>-0.3339</v>
       </c>
       <c r="V27" t="n">
         <v>-0.9658</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-8.3325</v>
+        <v>-8.473800000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.3708</v>
+        <v>-5.467</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.9616</v>
+        <v>-3.0069</v>
       </c>
       <c r="G28" t="n">
         <v>-6.2951</v>
@@ -2638,13 +2638,13 @@
         <v>1.6493</v>
       </c>
       <c r="S28" t="n">
-        <v>0.2509</v>
+        <v>0.1095</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1999</v>
+        <v>0.1037</v>
       </c>
       <c r="U28" t="n">
-        <v>0.051</v>
+        <v>0.0058</v>
       </c>
       <c r="V28" t="n">
         <v>0.6439</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-29.5902</v>
+        <v>-28.9491</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.637900000000001</v>
+        <v>-2.6381</v>
       </c>
       <c r="F29" t="n">
-        <v>-26.952</v>
+        <v>-26.3112</v>
       </c>
       <c r="G29" t="n">
         <v>-27.3449</v>
@@ -2686,7 +2686,7 @@
         <v>-17.8884</v>
       </c>
       <c r="I29" t="n">
-        <v>-9.456300000000001</v>
+        <v>-9.456299999999999</v>
       </c>
       <c r="J29" t="n">
         <v>13.8703</v>
@@ -2695,7 +2695,7 @@
         <v>12.7459</v>
       </c>
       <c r="L29" t="n">
-        <v>1.124300000000001</v>
+        <v>1.1243</v>
       </c>
       <c r="M29" t="n">
         <v>-41.21499999999999</v>
@@ -2716,13 +2716,13 @@
         <v>21.9907</v>
       </c>
       <c r="S29" t="n">
-        <v>-3.3973</v>
+        <v>-2.7563</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1661</v>
+        <v>0.1663000000000001</v>
       </c>
       <c r="U29" t="n">
-        <v>-3.5635</v>
+        <v>-2.922499999999999</v>
       </c>
       <c r="V29" t="n">
         <v>-2.512999999999999</v>
